--- a/%PATH_EE267%/Documents/Resumes_final/job_apps.xlsx
+++ b/%PATH_EE267%/Documents/Resumes_final/job_apps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baron\Documents\Grad_School\EE_267\EE_267\%PATH_EE267%\Documents\Resumes_final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635823AF-41C7-4AB1-8C80-71751BCF684D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E4D3FC-2222-4F54-A7A8-54CF030F1081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{030A565E-7A5D-4697-A182-3556D0BC7B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -179,9 +179,6 @@
     <t>G Research</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Yes (1 Screening)</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t xml:space="preserve">FPGA Prototyping Engineer </t>
   </si>
   <si>
-    <t>Under Review</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
@@ -212,17 +206,50 @@
     <t>San Francisco</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>ChatGPT (OpenAI)</t>
+  </si>
+  <si>
+    <t>Airbus</t>
+  </si>
+  <si>
+    <t>FPGA Development Engineer</t>
+  </si>
+  <si>
+    <t>Madrid &lt;3</t>
+  </si>
+  <si>
+    <t>Experience (No Sponsorship)</t>
+  </si>
+  <si>
+    <t>Jane Street</t>
+  </si>
+  <si>
+    <t>Axelera AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe? </t>
+  </si>
+  <si>
+    <t>IONATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Software Enigneer </t>
+  </si>
+  <si>
+    <t>ALTEN Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJECTED </t>
+  </si>
+  <si>
+    <t>GHOSTED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +275,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="2" tint="-0.89999084444715716"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
       <family val="2"/>
@@ -256,15 +290,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="2" tint="-0.89999084444715716"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <color rgb="FFA66500"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -290,7 +323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -313,44 +346,31 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4C0552-0E39-4977-8B14-26A8BE7CBFF4}">
-  <dimension ref="B4:I21"/>
+  <dimension ref="B4:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
@@ -698,30 +718,30 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -733,7 +753,7 @@
       <c r="E5" s="2">
         <v>46092</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
@@ -747,7 +767,7 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="B6" s="12">
         <v>2</v>
       </c>
       <c r="C6" t="s">
@@ -759,7 +779,7 @@
       <c r="E6" s="2">
         <v>46093</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -773,7 +793,7 @@
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+      <c r="B7" s="12">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -785,7 +805,7 @@
       <c r="E7" s="2">
         <v>46094</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
@@ -799,7 +819,7 @@
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="5">
+      <c r="B8" s="11">
         <v>4</v>
       </c>
       <c r="C8" t="s">
@@ -811,7 +831,7 @@
       <c r="E8" s="2">
         <v>46097</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H8" s="3" t="s">
@@ -822,7 +842,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+      <c r="B9" s="12">
         <v>5</v>
       </c>
       <c r="C9" t="s">
@@ -834,7 +854,7 @@
       <c r="E9" s="2">
         <v>46097</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G9" t="s">
@@ -848,7 +868,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+      <c r="B10" s="12">
         <v>6</v>
       </c>
       <c r="C10" t="s">
@@ -860,7 +880,7 @@
       <c r="E10" s="2">
         <v>46097</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -871,7 +891,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="5">
+      <c r="B11" s="11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
@@ -883,8 +903,11 @@
       <c r="E11" s="2">
         <v>46097</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>27</v>
+      <c r="F11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>18</v>
@@ -894,7 +917,7 @@
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+      <c r="B12" s="12">
         <v>8</v>
       </c>
       <c r="C12" t="s">
@@ -906,7 +929,7 @@
       <c r="E12" s="2">
         <v>46097</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
@@ -916,11 +939,11 @@
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
+      <c r="B13" s="12">
         <v>9</v>
       </c>
       <c r="C13" t="s">
@@ -932,7 +955,7 @@
       <c r="E13" s="2">
         <v>46099</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -943,31 +966,31 @@
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="10">
-        <v>10</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="13">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="7">
         <v>46106</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="14" t="s">
+      <c r="F14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="4">
+      <c r="B15" s="12">
         <v>11</v>
       </c>
       <c r="C15" t="s">
@@ -979,8 +1002,8 @@
       <c r="E15" s="2">
         <v>46100</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>27</v>
+      <c r="F15" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>18</v>
@@ -990,7 +1013,7 @@
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
+      <c r="B16" s="12">
         <v>12</v>
       </c>
       <c r="C16" t="s">
@@ -1002,7 +1025,7 @@
       <c r="E16" s="2">
         <v>46100</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="5" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="3" t="s">
@@ -1013,7 +1036,7 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>13</v>
       </c>
       <c r="C17" t="s">
@@ -1025,7 +1048,7 @@
       <c r="E17" s="2">
         <v>46100</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G17" t="s">
@@ -1039,7 +1062,7 @@
       </c>
     </row>
     <row r="18" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="4">
+      <c r="B18" s="12">
         <v>14</v>
       </c>
       <c r="C18" t="s">
@@ -1051,8 +1074,8 @@
       <c r="E18" s="2">
         <v>46101</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>46</v>
+      <c r="F18" s="15" t="s">
+        <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>18</v>
@@ -1062,38 +1085,37 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="15">
+      <c r="B19" s="12">
         <v>15</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="2">
+        <v>46103</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="12">
-        <v>46103</v>
-      </c>
-      <c r="F19" s="16" t="s">
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="12">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="14" t="s">
+      <c r="D20" t="s">
         <v>51</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
       </c>
       <c r="E20" s="2">
         <v>46106</v>
@@ -1102,33 +1124,148 @@
         <v>27</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21">
+      <c r="B21" s="12">
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2">
         <v>46108</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="12">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
         <v>56</v>
       </c>
-      <c r="I21" t="s">
+      <c r="D22" t="s">
         <v>57</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46114</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="12">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46114</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="12">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46118</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="12">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46119</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
